--- a/docs/qa/NCKH_TestCase.xlsx
+++ b/docs/qa/NCKH_TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -2709,6 +2709,53 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2991485</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>60325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1470660</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>730885</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15884525" y="796925"/>
+          <a:ext cx="1496695" cy="670560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5071,6 +5118,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
